--- a/01-INTRO/M04/bus311-intro-m04-l01-lemonade-activity.xlsx
+++ b/01-INTRO/M04/bus311-intro-m04-l01-lemonade-activity.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R5cba92a8b8654956"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R456a5eb8af7e492c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 1 - Funding" sheetId="3" r:id="Rf12b8711f55146aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 2 - Investment" sheetId="4" r:id="R77607bcda3044f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year 1 - Operations" sheetId="5" r:id="R6ac3da2c72094796"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Five-Year Forecast" sheetId="6" r:id="R8ac3079b2a29439c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year 5 - Balance Sheet" sheetId="7" r:id="R7927281dfe0543f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluation &amp; Valuation" sheetId="8" r:id="Rbf52289f4da6466c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Checks" sheetId="9" r:id="R33f3c15d0d51479f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R179b84f9fae24dec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Rf4fc8e752ba941e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 1 - Funding" sheetId="3" r:id="Rcf9d865a538e4b2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 2 - Investment" sheetId="4" r:id="Rb1a5824f01f94366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year 1 - Operations" sheetId="5" r:id="R721a3b39328a443b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Five-Year Forecast" sheetId="6" r:id="R99b9e7e689994fa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year 5 - Balance Sheet" sheetId="7" r:id="Rdc5b81f777fd4354"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluation &amp; Valuation" sheetId="8" r:id="Rb1978e99b796472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Checks" sheetId="9" r:id="Rafd5f6a3a7844a52"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,13 +21,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="200" formatCode="$#,##0;[Red]($#,##0);-"/>
     <x:numFmt numFmtId="201" formatCode="#,##0;[Red](#,##0);-"/>
     <x:numFmt numFmtId="202" formatCode="0.0%;[Red](0.0%);-"/>
     <x:numFmt numFmtId="203" formatCode="$0.00;[Red]($0.00);-"/>
     <x:numFmt numFmtId="204" formatCode="0.0x;[Red](0.0x);-"/>
     <x:numFmt numFmtId="205" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <x:numFmt numFmtId="206" formatCode="$#,##0.00"/>
   </x:numFmts>
   <x:fonts count="12">
     <x:font>
@@ -285,7 +286,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="167">
+  <x:cellXfs count="169">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -609,6 +610,10 @@
     <x:xf numFmtId="205" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -620,7 +625,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -631,7 +636,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -642,7 +647,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -653,7 +658,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -664,7 +669,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -675,7 +680,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -686,7 +691,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -697,7 +702,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -708,7 +713,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -719,7 +724,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -730,7 +735,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -741,7 +746,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -752,7 +757,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -763,7 +768,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -774,7 +779,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -785,7 +790,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -796,7 +801,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -807,7 +812,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -818,7 +823,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -829,7 +834,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -840,7 +845,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -851,7 +856,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -862,7 +867,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -873,7 +878,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -884,7 +889,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -895,7 +900,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -906,7 +911,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -917,7 +922,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -928,7 +933,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -939,7 +944,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -950,7 +955,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -961,7 +966,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -972,7 +977,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -983,7 +988,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -994,7 +999,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -1005,7 +1010,7 @@
         <x:color rgb="FF1F6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -1231,9 +1236,9 @@
       <x:c r="G1" s="5"/>
       <x:c r="H1" s="5"/>
     </x:row>
-    <x:row r="2" ht="28" customHeight="1">
+    <x:row r="2" ht="44" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>M04 Apply activity: connect financing, operations, cash flow, performance, and valuation.</x:v>
+        <x:v>Reserved for later use — not assigned in M04. Trace an existing model of financing, operations, cash flow, and value.</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -1300,9 +1305,9 @@
       <x:c r="G7" s="17"/>
       <x:c r="H7" s="17"/>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="56" customHeight="1">
       <x:c r="A8" s="30" t="str">
-        <x:v>Build the video case into a linked financial model, explain why profit and cash differ, assess growth and financing risk, and connect earnings to value. Submit the completed workbook plus concise responses to the five interpretation prompts on Evaluation &amp; Valuation.</x:v>
+        <x:v>When assigned: enter the case assumptions, trace the supplied formulas, and explain profit versus cash and financing risk. Valuation and dilution are a later stage after those topics are taught.</x:v>
       </x:c>
       <x:c r="B8" s="31"/>
       <x:c r="C8" s="31"/>
@@ -1334,7 +1339,7 @@
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="17" t="str">
-        <x:v>50-minute activity roadmap</x:v>
+        <x:v>Staged application — schedule to be confirmed</x:v>
       </x:c>
       <x:c r="B11" s="17"/>
       <x:c r="C11" s="17"/>
@@ -1346,7 +1351,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="38" t="str">
-        <x:v>Time</x:v>
+        <x:v>Stage</x:v>
       </x:c>
       <x:c r="B12" s="38" t="str">
         <x:v>What you will do</x:v>
@@ -1360,12 +1365,12 @@
       <x:c r="G12" s="38"/>
       <x:c r="H12" s="38"/>
     </x:row>
-    <x:row r="13" ht="26" customHeight="1">
+    <x:row r="13" ht="38" customHeight="1">
       <x:c r="A13" s="39" t="str">
-        <x:v>0-5 min</x:v>
+        <x:v>Before session</x:v>
       </x:c>
       <x:c r="B13" s="39" t="str">
-        <x:v>Open the video and scan this workbook.</x:v>
+        <x:v>Watch the video and capture base assumptions.</x:v>
       </x:c>
       <x:c r="C13" s="39" t="str">
         <x:v>Know the tab sequence and input legend.</x:v>
@@ -1376,12 +1381,12 @@
       <x:c r="G13" s="39"/>
       <x:c r="H13" s="39"/>
     </x:row>
-    <x:row r="14" ht="26" customHeight="1">
+    <x:row r="14" ht="38" customHeight="1">
       <x:c r="A14" s="39" t="str">
-        <x:v>5-15 min</x:v>
+        <x:v>Stage A</x:v>
       </x:c>
       <x:c r="B14" s="39" t="str">
-        <x:v>Capture the case assumptions from the video.</x:v>
+        <x:v>Trace funding, investment, operations, and cash.</x:v>
       </x:c>
       <x:c r="C14" s="39" t="str">
         <x:v>Assumptions status changes to READY.</x:v>
@@ -1392,12 +1397,12 @@
       <x:c r="G14" s="39"/>
       <x:c r="H14" s="39"/>
     </x:row>
-    <x:row r="15" ht="26" customHeight="1">
+    <x:row r="15" ht="38" customHeight="1">
       <x:c r="A15" s="39" t="str">
-        <x:v>15-30 min</x:v>
+        <x:v>Stage A</x:v>
       </x:c>
       <x:c r="B15" s="39" t="str">
-        <x:v>Trace funding, investment, and Year-1 operations.</x:v>
+        <x:v>Explain gross versus net profit and cash.</x:v>
       </x:c>
       <x:c r="C15" s="39" t="str">
         <x:v>All three statement checks show PASS.</x:v>
@@ -1408,12 +1413,12 @@
       <x:c r="G15" s="39"/>
       <x:c r="H15" s="39"/>
     </x:row>
-    <x:row r="16" ht="26" customHeight="1">
+    <x:row r="16" ht="38" customHeight="1">
       <x:c r="A16" s="39" t="str">
-        <x:v>30-40 min</x:v>
+        <x:v>Stage B</x:v>
       </x:c>
       <x:c r="B16" s="39" t="str">
-        <x:v>Review the five-year forecast and valuation.</x:v>
+        <x:v>Test lower unit growth at fixed expansion.</x:v>
       </x:c>
       <x:c r="C16" s="39" t="str">
         <x:v>Year-5 cash, balance sheet, and valuation connect.</x:v>
@@ -1424,12 +1429,12 @@
       <x:c r="G16" s="39"/>
       <x:c r="H16" s="39"/>
     </x:row>
-    <x:row r="17" ht="26" customHeight="1">
+    <x:row r="17" ht="38" customHeight="1">
       <x:c r="A17" s="39" t="str">
-        <x:v>40-50 min</x:v>
+        <x:v>Later valuation</x:v>
       </x:c>
       <x:c r="B17" s="39" t="str">
-        <x:v>Complete the sensitivity and interpretation prompts.</x:v>
+        <x:v>Interpret share price and primary versus secondary transactions.</x:v>
       </x:c>
       <x:c r="C17" s="39" t="str">
         <x:v>Submit one finished workbook.</x:v>
@@ -1483,7 +1488,7 @@
         <x:v>Assumptions</x:v>
       </x:c>
       <x:c r="B21" s="39" t="str">
-        <x:v>Enter only the yellow cells using the video.</x:v>
+        <x:v>Enter base video inputs in yellow cells; enter downside growth when Stage B is assigned.</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:v>The status reads READY.</x:v>
@@ -1566,7 +1571,7 @@
         <x:v>Interpret performance, value, and dilution.</x:v>
       </x:c>
       <x:c r="C26" s="39" t="str">
-        <x:v>All five responses are complete.</x:v>
+        <x:v>Stage A: prompts 1, 3, 4. Stage B: prompt 2. Later valuation: prompt 5.</x:v>
       </x:c>
       <x:c r="D26" s="39"/>
       <x:c r="E26" s="39"/>
@@ -1850,7 +1855,7 @@
         <x:v>MODEL STATUS</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:f>IF(COUNT(B7:B12)+COUNT(B15:B26)+COUNT(B29:F29)+COUNT(B33)&lt;24,"ENTER VIDEO INPUTS","READY")</x:f>
+        <x:f>IF(COUNT(B7:B12)+COUNT(B15:B26)+COUNT(B29:F29)&lt;23,"ENTER VIDEO INPUTS","READY")</x:f>
         <x:v>ENTER VIDEO INPUTS</x:v>
       </x:c>
       <x:c r="C3" s="1"/>
@@ -2444,6 +2449,12 @@
     <x:cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="WAITING"/>
     <x:cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="READY"/>
   </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="decimal" operator="between" sqref="B33">
+      <x:formula1>0</x:formula1>
+      <x:formula2>B22</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -4561,7 +4572,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="107" t="str">
-        <x:v>Expansion capex</x:v>
+        <x:v>Ending cash</x:v>
       </x:c>
       <x:c r="B33" s="107"/>
       <x:c r="C33" s="129" t="str">
@@ -4583,7 +4594,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="1" t="str">
-        <x:v>Ending cash</x:v>
+        <x:v>Gross fixed assets</x:v>
       </x:c>
       <x:c r="B34" s="1"/>
       <x:c r="C34" s="104" t="str">
@@ -4605,7 +4616,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="1" t="str">
-        <x:v>Gross fixed assets</x:v>
+        <x:v>Accumulated depreciation</x:v>
       </x:c>
       <x:c r="B35" s="1"/>
       <x:c r="C35" s="103" t="str">
@@ -4627,7 +4638,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="107" t="str">
-        <x:v>Accumulated depreciation</x:v>
+        <x:v>Net fixed assets</x:v>
       </x:c>
       <x:c r="B36" s="107"/>
       <x:c r="C36" s="108" t="str">
@@ -4649,7 +4660,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="1" t="str">
-        <x:v>Net fixed assets</x:v>
+        <x:v>Founder idea / illustrative intangible</x:v>
       </x:c>
       <x:c r="B37" s="1"/>
       <x:c r="C37" s="104" t="str">
@@ -4671,7 +4682,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="107" t="str">
-        <x:v>Founder idea / illustrative intangible</x:v>
+        <x:v>Total assets</x:v>
       </x:c>
       <x:c r="B38" s="107"/>
       <x:c r="C38" s="129" t="str">
@@ -4693,7 +4704,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="1" t="str">
-        <x:v>Total assets</x:v>
+        <x:v>Debt</x:v>
       </x:c>
       <x:c r="B39" s="1"/>
       <x:c r="C39" s="104" t="str">
@@ -4715,7 +4726,7 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="1" t="str">
-        <x:v>Debt</x:v>
+        <x:v>Contributed capital</x:v>
       </x:c>
       <x:c r="B40" s="1"/>
       <x:c r="C40" s="104" t="str">
@@ -4737,7 +4748,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="1" t="str">
-        <x:v>Contributed capital</x:v>
+        <x:v>Retained earnings</x:v>
       </x:c>
       <x:c r="B41" s="1"/>
       <x:c r="C41" s="103" t="str">
@@ -4759,7 +4770,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="107" t="str">
-        <x:v>Retained earnings</x:v>
+        <x:v>Total equity</x:v>
       </x:c>
       <x:c r="B42" s="107"/>
       <x:c r="C42" s="108" t="str">
@@ -4781,7 +4792,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="107" t="str">
-        <x:v>Total equity</x:v>
+        <x:v>Total liabilities + equity</x:v>
       </x:c>
       <x:c r="B43" s="107"/>
       <x:c r="C43" s="108" t="str">
@@ -4803,7 +4814,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="1" t="str">
-        <x:v>Total liabilities + equity</x:v>
+        <x:v>Balance check</x:v>
       </x:c>
       <x:c r="B44" s="1"/>
       <x:c r="C44" s="103" t="str">
@@ -4824,9 +4835,7 @@
       <x:c r="H44" s="1"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="1" t="str">
-        <x:v>Balance check</x:v>
-      </x:c>
+      <x:c r="A45" s="1"/>
       <x:c r="B45" s="1"/>
       <x:c r="C45" s="1"/>
       <x:c r="D45" s="1"/>
@@ -4835,19 +4844,31 @@
       <x:c r="G45" s="1"/>
       <x:c r="H45" s="1"/>
     </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="1"/>
+    <x:row r="46" ht="28" customHeight="1">
+      <x:c r="A46" s="1" t="str">
+        <x:v>Expansion capex (cash outflow)</x:v>
+      </x:c>
       <x:c r="B46" s="1"/>
-      <x:c r="C46" s="1"/>
-      <x:c r="D46" s="1"/>
-      <x:c r="E46" s="1"/>
-      <x:c r="F46" s="1"/>
-      <x:c r="G46" s="1"/>
+      <x:c r="C46" s="167" t="str">
+        <x:f>IF(C7="","",C8*'Assumptions'!$B$15)</x:f>
+      </x:c>
+      <x:c r="D46" s="167" t="str">
+        <x:f>IF(D7="","",D8*'Assumptions'!$B$15)</x:f>
+      </x:c>
+      <x:c r="E46" s="167" t="str">
+        <x:f>IF(E7="","",E8*'Assumptions'!$B$15)</x:f>
+      </x:c>
+      <x:c r="F46" s="167" t="str">
+        <x:f>IF(F7="","",F8*'Assumptions'!$B$15)</x:f>
+      </x:c>
+      <x:c r="G46" s="167" t="str">
+        <x:f>IF(G7="","",G8*'Assumptions'!$B$15)</x:f>
+      </x:c>
       <x:c r="H46" s="1"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="65" t="str">
-        <x:v>Forecast convention: the initial Year-1 stand purchase appears on Day 2, outside this operating roll-forward. Expansion capex begins in Year 2. Inventory is consumed in Year 1 and is not replenished in this simplified case, so working capital is not a continuing forecast driver.</x:v>
+        <x:v>Cash rolls forward from operations less expansion capex (row 46). Year-1 stand purchase is on Day 2. Expansion is fixed, not cash-triggered. Inventory release is a simplified assumption; ongoing working capital is not forecast.</x:v>
       </x:c>
       <x:c r="B47" s="66"/>
       <x:c r="C47" s="66"/>
@@ -5324,7 +5345,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>Measure performance carefully, then distinguish company financing from a shareholder sale.</x:v>
+        <x:v>Stage A: prompts 1, 3, 4. Stage B sensitivity: prompt 2. Later valuation: prompt 5 after instruction.</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -5723,9 +5744,9 @@
       <x:c r="G23" s="1"/>
       <x:c r="H23" s="1"/>
     </x:row>
-    <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="17" t="str">
-        <x:v>One-variable sensitivity: unit-volume growth</x:v>
+    <x:row r="24" ht="46" customHeight="1">
+      <x:c r="A24" s="168" t="str">
+        <x:v>Sensitivity: lower unit growth; fixed stand expansion (not a funding-feasibility test)</x:v>
       </x:c>
       <x:c r="B24" s="17"/>
       <x:c r="C24" s="17"/>
@@ -5761,10 +5782,10 @@
         <x:f>IF('Assumptions'!B3&lt;&gt;"READY","",'Assumptions'!B22)</x:f>
       </x:c>
       <x:c r="C26" s="131" t="str">
-        <x:f>IF('Assumptions'!B3&lt;&gt;"READY","",'Assumptions'!B33)</x:f>
+        <x:f>IF(OR('Assumptions'!B3&lt;&gt;"READY",NOT(ISNUMBER('Assumptions'!B33))),"",'Assumptions'!B33)</x:f>
       </x:c>
       <x:c r="D26" s="110" t="str">
-        <x:f>IF(B26="","",C26-B26)</x:f>
+        <x:f>IF(COUNT(B26:C26)&lt;2,"",C26-B26)</x:f>
       </x:c>
       <x:c r="E26" s="1"/>
       <x:c r="F26" s="1"/>
@@ -5779,10 +5800,10 @@
         <x:f>IF($B$7="","",$B$7)</x:f>
       </x:c>
       <x:c r="C27" s="104" t="str">
-        <x:f>IF('Assumptions'!B3&lt;&gt;"READY","",'Assumptions'!F29*('Assumptions'!B17*(1+'Assumptions'!B33)^4)*('Assumptions'!B18+'Assumptions'!B23*4))</x:f>
+        <x:f>IF(OR('Assumptions'!B3&lt;&gt;"READY",NOT(ISNUMBER('Assumptions'!B33))),"",'Assumptions'!F29*('Assumptions'!B17*(1+'Assumptions'!B33)^4)*('Assumptions'!B18+'Assumptions'!B23*4))</x:f>
       </x:c>
       <x:c r="D27" s="103" t="str">
-        <x:f>IF(B27="","",C27-B27)</x:f>
+        <x:f>IF(COUNT(B27:C27)&lt;2,"",C27-B27)</x:f>
       </x:c>
       <x:c r="E27" s="1"/>
       <x:c r="F27" s="1"/>
@@ -5797,10 +5818,10 @@
         <x:f>IF($B$8="","",$B$8)</x:f>
       </x:c>
       <x:c r="C28" s="104" t="str">
-        <x:f>IF('Assumptions'!B3&lt;&gt;"READY","",C27-('Assumptions'!F29*('Assumptions'!B17*(1+'Assumptions'!B33)^4)*'Assumptions'!B20)-('Assumptions'!F29*'Assumptions'!B19)-('Assumptions'!F29*('Assumptions'!B15/'Assumptions'!B21)))</x:f>
+        <x:f>IF(OR('Assumptions'!B3&lt;&gt;"READY",NOT(ISNUMBER('Assumptions'!B33))),"",C27-('Assumptions'!F29*('Assumptions'!B17*(1+'Assumptions'!B33)^4)*'Assumptions'!B20)-('Assumptions'!F29*'Assumptions'!B19)-('Assumptions'!F29*('Assumptions'!B15/'Assumptions'!B21)))</x:f>
       </x:c>
       <x:c r="D28" s="103" t="str">
-        <x:f>IF(B28="","",C28-B28)</x:f>
+        <x:f>IF(COUNT(B28:C28)&lt;2,"",C28-B28)</x:f>
       </x:c>
       <x:c r="E28" s="1"/>
       <x:c r="F28" s="1"/>
@@ -5815,10 +5836,10 @@
         <x:f>IF($B$10="","",$B$10)</x:f>
       </x:c>
       <x:c r="C29" s="104" t="str">
-        <x:f>IF('Assumptions'!B3&lt;&gt;"READY","",(C28-('Assumptions'!B10*'Assumptions'!B11))*(1-'Assumptions'!B24))</x:f>
+        <x:f>IF(OR('Assumptions'!B3&lt;&gt;"READY",NOT(ISNUMBER('Assumptions'!B33))),"",(C28-'Assumptions'!B10*'Assumptions'!B11)-MAX(C28-'Assumptions'!B10*'Assumptions'!B11,0)*'Assumptions'!B24)</x:f>
       </x:c>
       <x:c r="D29" s="103" t="str">
-        <x:f>IF(B29="","",C29-B29)</x:f>
+        <x:f>IF(COUNT(B29:C29)&lt;2,"",C29-B29)</x:f>
       </x:c>
       <x:c r="E29" s="1"/>
       <x:c r="F29" s="1"/>
@@ -5833,10 +5854,10 @@
         <x:f>IF($B$18="","",$B$18)</x:f>
       </x:c>
       <x:c r="C30" s="104" t="str">
-        <x:f>IF('Assumptions'!B3&lt;&gt;"READY","",(C29/('Assumptions'!B7+'Assumptions'!B8))*'Assumptions'!B25*('Assumptions'!B7+'Assumptions'!B8))</x:f>
+        <x:f>IF(OR('Assumptions'!B3&lt;&gt;"READY",NOT(ISNUMBER('Assumptions'!B33))),"",(C29/('Assumptions'!B7+'Assumptions'!B8))*'Assumptions'!B25*('Assumptions'!B7+'Assumptions'!B8))</x:f>
       </x:c>
       <x:c r="D30" s="103" t="str">
-        <x:f>IF(B30="","",C30-B30)</x:f>
+        <x:f>IF(COUNT(B30:C30)&lt;2,"",C30-B30)</x:f>
       </x:c>
       <x:c r="E30" s="1"/>
       <x:c r="F30" s="1"/>
@@ -5865,7 +5886,7 @@
     </x:row>
     <x:row r="33" ht="22" customHeight="1">
       <x:c r="A33" s="17" t="str">
-        <x:v>Interpretation prompts - complete all five</x:v>
+        <x:v>Interpretation prompts — complete the assigned stage</x:v>
       </x:c>
       <x:c r="B33" s="17"/>
       <x:c r="C33" s="17"/>
@@ -5927,9 +5948,9 @@
       <x:c r="G38" s="1"/>
       <x:c r="H38" s="1"/>
     </x:row>
-    <x:row r="39">
+    <x:row r="39" ht="52" customHeight="1">
       <x:c r="A39" s="139" t="str">
-        <x:v>2. Which operating assumption contributes most to Year-5 EBIT growth, and why?</x:v>
+        <x:v>2. With the stand schedule fixed, how does lower unit-volume growth change Year-5 EBIT? Explain the cost behavior; do not claim this ranks every growth driver.</x:v>
       </x:c>
       <x:c r="B39" s="139"/>
       <x:c r="C39" s="139"/>
@@ -6290,14 +6311,14 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="39" t="str">
-        <x:v>Required inputs populated</x:v>
+        <x:v>Base inputs populated</x:v>
       </x:c>
       <x:c r="B7" s="166" t="n">
-        <x:f>COUNT('Assumptions'!B7:B12)+COUNT('Assumptions'!B15:B26)+COUNT('Assumptions'!B29:F29)+COUNT('Assumptions'!B33)</x:f>
+        <x:f>COUNT('Assumptions'!B7:B12)+COUNT('Assumptions'!B15:B26)+COUNT('Assumptions'!B29:F29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C7" s="166" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D7" s="166" t="str">
         <x:f>IF('Assumptions'!$B$3&lt;&gt;"READY","",B7-C7)</x:f>
@@ -6590,7 +6611,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="30" t="str">
-        <x:v>A PASS status means the model is internally consistent. It does not mean every accounting assumption is universally correct. The tax-benefit and illustrative-intangible judgments remain visible for interpretation.</x:v>
+        <x:v>PASS tests base-input completeness and internal consistency, not interpretation responses, financing feasibility, or accounting-policy validity. Complete the later sensitivity and prompts when assigned.</x:v>
       </x:c>
       <x:c r="B19" s="31"/>
       <x:c r="C19" s="31"/>
